--- a/artfynd/A 61386-2022 artfynd.xlsx
+++ b/artfynd/A 61386-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61386-2022 artfynd.xlsx
+++ b/artfynd/A 61386-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111357157</v>
+        <v>111356762</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553906.6257793424</v>
+        <v>553952</v>
       </c>
       <c r="R2" t="n">
-        <v>7001993.497915561</v>
+        <v>7002045</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111357015</v>
+        <v>111357080</v>
       </c>
       <c r="B3" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553909.463631961</v>
+        <v>553907</v>
       </c>
       <c r="R3" t="n">
-        <v>7002013.443953016</v>
+        <v>7001993</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111357080</v>
+        <v>111357360</v>
       </c>
       <c r="B4" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553906.6257793424</v>
+        <v>553855</v>
       </c>
       <c r="R4" t="n">
-        <v>7001993.497915561</v>
+        <v>7001983</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111357360</v>
+        <v>111357015</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553854.7258749125</v>
+        <v>553910</v>
       </c>
       <c r="R5" t="n">
-        <v>7001982.684500803</v>
+        <v>7002013</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,37 +1107,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111356256</v>
+        <v>111356354</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554052.9808952439</v>
+        <v>554027</v>
       </c>
       <c r="R6" t="n">
-        <v>7002124.374295473</v>
+        <v>7002090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,12 +1218,7 @@
         <v>111356632</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553994.858156529</v>
+        <v>553995</v>
       </c>
       <c r="R7" t="n">
-        <v>7002052.403435753</v>
+        <v>7002053</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1353,37 +1323,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111358027</v>
+        <v>111357157</v>
       </c>
       <c r="B8" t="n">
-        <v>98446</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553857.5193624865</v>
+        <v>553907</v>
       </c>
       <c r="R8" t="n">
-        <v>7002168.599353628</v>
+        <v>7001993</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111357873</v>
+        <v>111357776</v>
       </c>
       <c r="B9" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553818.3826172169</v>
+        <v>553809</v>
       </c>
       <c r="R9" t="n">
-        <v>7002180.158265028</v>
+        <v>7002131</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1579,37 +1539,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111356702</v>
+        <v>111357873</v>
       </c>
       <c r="B10" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105336</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553981.1551737323</v>
+        <v>553818</v>
       </c>
       <c r="R10" t="n">
-        <v>7002032.27630965</v>
+        <v>7002181</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,51 +1647,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111356314</v>
+        <v>111356520</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kraftverket, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554037.1883795768</v>
+        <v>554017</v>
       </c>
       <c r="R11" t="n">
-        <v>7002120.944976788</v>
+        <v>7002041</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,37 +1763,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111357776</v>
+        <v>111356702</v>
       </c>
       <c r="B12" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>105336</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553808.7819238321</v>
+        <v>553982</v>
       </c>
       <c r="R12" t="n">
-        <v>7002131.15853373</v>
+        <v>7002033</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,37 +1871,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111358006</v>
+        <v>111356256</v>
       </c>
       <c r="B13" t="n">
-        <v>98446</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553854.1622618367</v>
+        <v>554053</v>
       </c>
       <c r="R13" t="n">
-        <v>7002179.849007829</v>
+        <v>7002124</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1994,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,15 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111356587</v>
+        <v>111356263</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,10 +2015,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553994.858156529</v>
+        <v>554055</v>
       </c>
       <c r="R14" t="n">
-        <v>7002052.403435753</v>
+        <v>7002114</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2107,7 +2050,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2060,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,37 +2087,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111356762</v>
+        <v>111356314</v>
       </c>
       <c r="B15" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553951.9614282879</v>
+        <v>554037</v>
       </c>
       <c r="R15" t="n">
-        <v>7002044.904499132</v>
+        <v>7002120</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,15 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111356263</v>
+        <v>111356587</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554054.0600129352</v>
+        <v>553995</v>
       </c>
       <c r="R16" t="n">
-        <v>7002113.991040959</v>
+        <v>7002053</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,37 +2303,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111356354</v>
+        <v>111357223</v>
       </c>
       <c r="B17" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2411,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554026.383447904</v>
+        <v>553915</v>
       </c>
       <c r="R17" t="n">
-        <v>7002090.012868459</v>
+        <v>7001973</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2446,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2384,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,12 +2414,7 @@
         <v>111357720</v>
       </c>
       <c r="B18" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553822.8840132115</v>
+        <v>553823</v>
       </c>
       <c r="R18" t="n">
-        <v>7002127.322982416</v>
+        <v>7002127</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2593,6 +2516,330 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111358006</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kraftverket, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553855</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7002179</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>111358027</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kraftverket, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>553858</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7002169</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111358078</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kraftverket, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>553898</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7002184</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61386-2022 artfynd.xlsx
+++ b/artfynd/A 61386-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356762</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357360</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356354</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356632</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357157</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357776</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357873</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356520</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356702</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356256</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2084,6 +2149,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356263</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356314</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2300,6 +2375,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111356587</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357223</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2516,6 +2601,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357720</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2624,6 +2714,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358006</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2732,6 +2827,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358027</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2840,8 +2940,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358078</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>